--- a/Excel/excel/data.xlsx
+++ b/Excel/excel/data.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\ProjectZoo\Excel\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04E8C8A-2A8C-4504-A778-124E336938DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1749AB-119E-45D9-AFEC-5BE2329CA5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5060" yWindow="3750" windowWidth="14400" windowHeight="8240" firstSheet="7" activeTab="7" xr2:uid="{6CCAADBB-0688-414B-A2F0-1AE5F5108BF8}"/>
+    <workbookView minimized="1" xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="9890" firstSheet="12" activeTab="15" xr2:uid="{6CCAADBB-0688-414B-A2F0-1AE5F5108BF8}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" firstSheet="15" activeTab="16" xr2:uid="{7E6C8D06-A8B5-450A-B350-CE12736167E4}"/>
   </bookViews>
   <sheets>
     <sheet name="card" sheetId="1" r:id="rId1"/>
@@ -28,6 +29,8 @@
     <sheet name="newBuff" sheetId="14" r:id="rId13"/>
     <sheet name="newBook" sheetId="13" r:id="rId14"/>
     <sheet name="newNegativeBuff" sheetId="15" r:id="rId15"/>
+    <sheet name="cardDesc" sheetId="16" r:id="rId16"/>
+    <sheet name="cardNew2" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -112,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3436" uniqueCount="1982">
   <si>
     <t>uid</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7431,6 +7434,351 @@
   </si>
   <si>
     <t>qiyeyouhuabumen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GainGold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得x点人气值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗x个食物。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽x张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弃x张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得x个木头。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得x个临时工人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得x个食物。如果某季度未执行过，下次额外获得x个。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个场馆视为与所有场馆相邻。</t>
+  </si>
+  <si>
+    <t>获得X点人气值，X为你的食物数量/x。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建造之后的x个季度之后拆除本场馆。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每与一个猿猴场馆相邻就获得x点人气值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得下x张猿猴场馆牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得食物时，额外获得x点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在商店进行购买后，获得x点人气值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每弃掉1张牌就获得x块钱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（每季度#limitUse次）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弃掉所有手牌，每张丢弃的牌获得1点食物，抽等量的牌。</t>
+  </si>
+  <si>
+    <t>弃掉所有手牌，每张丢弃的牌获得1块钱，抽等量的牌。</t>
+  </si>
+  <si>
+    <t>将你的1个普通工人升级，点数为x。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择1个场馆，复制x张牌到手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每弃掉1张牌就获得x个木头。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>猴子场馆消耗的食物量减x。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算相邻时，视为你有1个与所有场馆相邻的猴类场馆。</t>
+  </si>
+  <si>
+    <t>计算相邻时，2格以内的也算作相邻。</t>
+  </si>
+  <si>
+    <t>每弃掉1张牌就获得2点人气值。</t>
+  </si>
+  <si>
+    <t>每有1对相邻的猴子场馆，获得2食物。</t>
+  </si>
+  <si>
+    <t>获得X点人气值，X为本回合的弃牌数。</t>
+  </si>
+  <si>
+    <t>正面概率增加15%。</t>
+  </si>
+  <si>
+    <t>生成1个随机地块奖励。</t>
+  </si>
+  <si>
+    <t>获得1个木头。如果某季度未执行过，下次额外获得1个。</t>
+  </si>
+  <si>
+    <t>获得1张随机坏点子牌。</t>
+  </si>
+  <si>
+    <t>扩建2次。</t>
+  </si>
+  <si>
+    <t>获得4点人气值。本回合每获得过1次地块奖励，就额外获得3点人气值。</t>
+  </si>
+  <si>
+    <t>本季度所有爬虫场馆额外获得1点人气值。</t>
+  </si>
+  <si>
+    <t>获得X点人气值，X为地图上的地块奖励数。</t>
+  </si>
+  <si>
+    <t>contChinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>contEnglish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得#1点食物。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得#1金钱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得#1钢铁。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain #1 food.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain #1 coin(s).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有分数，有效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币，木头，铁，电力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币：点数1-3=》2个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁：点数6=》1个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽牌：点数456=》3选1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>木头：点数2-4=》2个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电力：any=》点数个</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升你的抽牌量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>·</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升你的选牌量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升你的金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升你的木头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升你的电力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升你的铁获取量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加工人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得4点聚财</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始获得钱，然后层数减一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽二选一，获得2点聚财</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将你的聚财翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丢弃1张牌，获得6点聚财</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接下来的3回合开始时，获得3木头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>热带雨林馆</t>
+  </si>
+  <si>
+    <t>热带雨林馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>草地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>湿地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沼泽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小湖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼缸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>笼子</t>
+  </si>
+  <si>
+    <t>笼子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻璃走廊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树屋</t>
+  </si>
+  <si>
+    <t>树屋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恒温室</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>极地馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海水浴缸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚克力水体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触摸池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>心情值10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果与另一种猿猴住在同一个场馆，对方得分翻倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵长目</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15块</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7438,7 +7786,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7479,6 +7827,15 @@
       <name val="Py"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -7512,7 +7869,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7523,6 +7880,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -19863,6 +20221,531 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A00BFE50-438D-4D4D-B281-7FEDB7F53E52}">
+  <dimension ref="A2:C43"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>773</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>758</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A390E7F-D032-4B7F-8A00-B113701EA9BC}">
+  <dimension ref="B3:G38"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="25.08203125" customWidth="1"/>
+    <col min="2" max="2" width="34.4140625" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="5" max="5" width="30.58203125" customWidth="1"/>
+    <col min="7" max="7" width="43.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7">
+      <c r="B3" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" t="s">
+        <v>1938</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="E14" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="G15" s="6" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1959</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" t="s">
+        <v>1944</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1960</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1961</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1962</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" t="s">
+        <v>1947</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1958</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1966</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" t="s">
+        <v>1950</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1969</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1970</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1971</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1972</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="E28" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="G29" s="6" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="G30" s="6" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="G31" s="6" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="33" spans="7:7">
+      <c r="G33" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="7:7">
+      <c r="G34" s="6" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="35" spans="7:7">
+      <c r="G35" s="6" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="36" spans="7:7">
+      <c r="G36" s="6" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="37" spans="7:7">
+      <c r="G37" s="6" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="38" spans="7:7">
+      <c r="G38" s="6" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE6872E-FB28-44F1-8AFD-A68325822C3A}">
   <dimension ref="A2:U31"/>
